--- a/out_gpfpran.xlsx
+++ b/out_gpfpran.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>SLNO</t>
   </si>
@@ -29,6 +29,9 @@
     <t>PIS</t>
   </si>
   <si>
+    <t>BANK_ACCNO</t>
+  </si>
+  <si>
     <t>GPF-1111</t>
   </si>
   <si>
@@ -41,6 +44,9 @@
     <t>2008AE10</t>
   </si>
   <si>
+    <t>10000000001</t>
+  </si>
+  <si>
     <t>GPF-2222</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
     <t>2008AE12</t>
   </si>
   <si>
+    <t>10000000010</t>
+  </si>
+  <si>
     <t>PRAN-3333</t>
   </si>
   <si>
@@ -63,6 +72,9 @@
   </si>
   <si>
     <t>2012BC24</t>
+  </si>
+  <si>
+    <t>10000000003</t>
   </si>
   <si>
     <t>UNKNOWN-99</t>
@@ -117,7 +129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -136,22 +148,28 @@
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -159,16 +177,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -176,16 +197,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -193,16 +217,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
